--- a/src/main/resources/datasets/import_projet_sample.xlsx
+++ b/src/main/resources/datasets/import_projet_sample.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>Identifiant</t>
   </si>
@@ -94,13 +94,13 @@
     </r>
   </si>
   <si>
-    <t>pascal.gibut@siamois.fr</t>
+    <t>Pascal Gibut</t>
   </si>
   <si>
     <t>chartres</t>
   </si>
   <si>
-    <t>duflos.franck@siamois.fr, pascal.gibut@siamois.fr</t>
+    <t>Franck Duflos, Pascal Gibut</t>
   </si>
   <si>
     <t>C309_01</t>
@@ -155,17 +155,6 @@
         <rFont val="Helvetica Neue"/>
       </rPr>
       <t>https://thesaurus.mom.fr/?idc=4287997&amp;idt=th252</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="10"/>
-        <color indexed="14"/>
-        <rFont val="Helvetica Neue"/>
-      </rPr>
-      <t>pascal.gibut@siamois.fr</t>
     </r>
   </si>
   <si>
@@ -238,7 +227,7 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="59" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -290,12 +279,6 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <u val="single"/>
-      <sz val="10"/>
-      <color indexed="14"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
@@ -334,13 +317,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="15"/>
+        <fgColor indexed="14"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="18"/>
+        <fgColor indexed="17"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -505,7 +488,22 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="15"/>
+      </left>
+      <right style="thin">
+        <color indexed="15"/>
+      </right>
+      <top style="thin">
+        <color indexed="15"/>
+      </top>
+      <bottom style="thin">
         <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="15"/>
       </left>
       <right style="thin">
         <color indexed="16"/>
@@ -514,7 +512,7 @@
         <color indexed="16"/>
       </top>
       <bottom style="thin">
-        <color indexed="17"/>
+        <color indexed="15"/>
       </bottom>
       <diagonal/>
     </border>
@@ -523,28 +521,43 @@
         <color indexed="16"/>
       </left>
       <right style="thin">
-        <color indexed="17"/>
+        <color indexed="15"/>
       </right>
       <top style="thin">
-        <color indexed="17"/>
+        <color indexed="16"/>
       </top>
       <bottom style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="17"/>
+        <color indexed="15"/>
+      </left>
+      <right style="thin">
+        <color indexed="15"/>
+      </right>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="15"/>
       </left>
       <right style="thin">
         <color indexed="16"/>
       </right>
       <top style="thin">
-        <color indexed="17"/>
+        <color indexed="15"/>
       </top>
       <bottom style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </bottom>
       <diagonal/>
     </border>
@@ -553,70 +566,40 @@
         <color indexed="16"/>
       </left>
       <right style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </right>
       <top style="thin">
-        <color indexed="17"/>
+        <color indexed="15"/>
       </top>
       <bottom style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </left>
       <right style="thin">
-        <color indexed="17"/>
+        <color indexed="15"/>
       </right>
       <top style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </top>
       <bottom style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="17"/>
+        <color indexed="15"/>
       </left>
       <right style="thin">
         <color indexed="16"/>
       </right>
       <top style="thin">
-        <color indexed="16"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="16"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="16"/>
-      </left>
-      <right style="thin">
-        <color indexed="16"/>
-      </right>
-      <top style="thin">
-        <color indexed="16"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="16"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="16"/>
-      </left>
-      <right style="thin">
-        <color indexed="17"/>
-      </right>
-      <top style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -628,13 +611,13 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </right>
       <top style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </top>
       <bottom style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,10 +626,10 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </right>
       <top style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
@@ -678,7 +661,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="16"/>
+        <color indexed="15"/>
       </right>
       <top style="thin">
         <color indexed="10"/>
@@ -705,7 +688,7 @@
       </left>
       <right/>
       <top style="thin">
-        <color indexed="17"/>
+        <color indexed="16"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -714,7 +697,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="17"/>
+        <color indexed="16"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -725,7 +708,7 @@
         <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="17"/>
+        <color indexed="16"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -803,7 +786,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -870,13 +853,16 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -888,7 +874,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -897,13 +883,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -918,13 +904,13 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -991,7 +977,6 @@
       <rgbColor rgb="ff9a9a9a"/>
       <rgbColor rgb="ff0000ff"/>
       <rgbColor rgb="ffd4d4d4"/>
-      <rgbColor rgb="ff1155cc"/>
       <rgbColor rgb="ffbdc0bf"/>
       <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff3f3f3f"/>
@@ -2039,7 +2024,7 @@
     <col min="4" max="4" width="44.8516" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.6719" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.3516" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.2266" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.6719" style="1" customWidth="1"/>
     <col min="9" max="9" width="45.6719" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.8516" style="1" customWidth="1"/>
@@ -17185,14 +17170,14 @@
       <c r="E2" t="s" s="21">
         <v>19</v>
       </c>
-      <c r="F2" t="s" s="14">
-        <v>34</v>
+      <c r="F2" t="s" s="22">
+        <v>18</v>
       </c>
-      <c r="G2" t="s" s="14">
-        <v>34</v>
+      <c r="G2" t="s" s="22">
+        <v>18</v>
       </c>
       <c r="H2" t="s" s="21">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="14.7" customHeight="1">
@@ -17200,19 +17185,19 @@
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
       <c r="D3" t="s" s="20">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s" s="21">
         <v>19</v>
       </c>
-      <c r="F3" t="s" s="14">
-        <v>34</v>
+      <c r="F3" t="s" s="22">
+        <v>18</v>
       </c>
-      <c r="G3" t="s" s="14">
-        <v>34</v>
+      <c r="G3" t="s" s="22">
+        <v>18</v>
       </c>
       <c r="H3" t="s" s="21">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="14.7" customHeight="1">
@@ -17220,19 +17205,19 @@
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
       <c r="D4" t="s" s="20">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s" s="21">
         <v>19</v>
       </c>
-      <c r="F4" t="s" s="14">
-        <v>34</v>
+      <c r="F4" t="s" s="22">
+        <v>18</v>
       </c>
-      <c r="G4" t="s" s="14">
-        <v>34</v>
+      <c r="G4" t="s" s="22">
+        <v>18</v>
       </c>
       <c r="H4" t="s" s="21">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="13.65" customHeight="1">
@@ -26659,14 +26644,8 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4286251&amp;idt=th252"/>
     <hyperlink ref="D2" r:id="rId2" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287997&amp;idt=th252"/>
-    <hyperlink ref="F2" r:id="rId3" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
-    <hyperlink ref="G2" r:id="rId4" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
-    <hyperlink ref="D3" r:id="rId5" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287998&amp;idt=th252"/>
-    <hyperlink ref="F3" r:id="rId6" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
-    <hyperlink ref="G3" r:id="rId7" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
-    <hyperlink ref="D4" r:id="rId8" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287999&amp;idt=th252"/>
-    <hyperlink ref="F4" r:id="rId9" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
-    <hyperlink ref="G4" r:id="rId10" location="" tooltip="" display="pascal.gibut@siamois.fr"/>
+    <hyperlink ref="D3" r:id="rId3" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287998&amp;idt=th252"/>
+    <hyperlink ref="D4" r:id="rId4" location="" tooltip="" display="https://thesaurus.mom.fr/?idc=4287999&amp;idt=th252"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -26684,528 +26663,528 @@
   <dimension ref="A1:E73"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.45" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="16.3516" style="22" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="22" customWidth="1"/>
+    <col min="1" max="5" width="16.3516" style="23" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.2" customHeight="1">
-      <c r="A1" t="s" s="23">
+      <c r="A1" t="s" s="24">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="24">
         <v>39</v>
       </c>
-      <c r="B1" t="s" s="23">
-        <v>40</v>
-      </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" ht="13.2" customHeight="1">
-      <c r="A2" t="s" s="25">
+      <c r="A2" t="s" s="26">
         <v>13</v>
       </c>
-      <c r="B2" t="s" s="26">
+      <c r="B2" t="s" s="27">
         <v>22</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="31"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="28"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
     </row>
     <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
     </row>
     <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
     </row>
     <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="28"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
     </row>
     <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
     </row>
     <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="28"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
     </row>
     <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="28"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
     </row>
     <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="28"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
     </row>
     <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
     </row>
     <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="28"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
     </row>
     <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
     </row>
     <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="28"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
     </row>
     <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="28"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
     </row>
     <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="28"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
     </row>
     <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="28"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
     </row>
     <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="28"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
     </row>
     <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
     </row>
     <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="28"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
     </row>
     <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="28"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
     </row>
     <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="28"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
     </row>
     <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="28"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
     </row>
     <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="28"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
     </row>
     <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="28"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
     </row>
     <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="28"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
     </row>
     <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="28"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
     </row>
     <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="28"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
     </row>
     <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
     </row>
     <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="33"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
     </row>
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="17"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
     </row>
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="2"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
     </row>
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="2"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
     </row>
     <row r="52" ht="13" customHeight="1">
       <c r="A52" s="2"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
     </row>
     <row r="53" ht="13" customHeight="1">
       <c r="A53" s="2"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
     </row>
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="2"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
+      <c r="B54" s="35"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
     </row>
     <row r="55" ht="13" customHeight="1">
       <c r="A55" s="2"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
     </row>
     <row r="56" ht="13" customHeight="1">
       <c r="A56" s="2"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
     </row>
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="2"/>
-      <c r="B57" s="34"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
     </row>
     <row r="58" ht="13" customHeight="1">
       <c r="A58" s="2"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
     </row>
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="2"/>
-      <c r="B59" s="34"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
     </row>
     <row r="60" ht="13" customHeight="1">
       <c r="A60" s="2"/>
-      <c r="B60" s="34"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
     </row>
     <row r="61" ht="13" customHeight="1">
       <c r="A61" s="2"/>
-      <c r="B61" s="34"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
     </row>
     <row r="62" ht="13" customHeight="1">
       <c r="A62" s="2"/>
-      <c r="B62" s="34"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="31"/>
     </row>
     <row r="63" ht="13" customHeight="1">
       <c r="A63" s="10"/>
-      <c r="B63" s="34"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
+      <c r="B63" s="35"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
     </row>
     <row r="64" ht="13" customHeight="1">
       <c r="A64" s="17"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
     </row>
     <row r="65" ht="13" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
     </row>
     <row r="66" ht="13" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
     </row>
     <row r="67" ht="13" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
     </row>
     <row r="68" ht="13" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
     </row>
     <row r="69" ht="13" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
     </row>
     <row r="70" ht="13" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
     </row>
     <row r="71" ht="13" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="31"/>
     </row>
     <row r="72" ht="13" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
     </row>
     <row r="73" ht="13" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="31"/>
+      <c r="E73" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
@@ -27224,437 +27203,437 @@
   <dimension ref="A1:F50"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.45" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.6719" style="37" customWidth="1"/>
-    <col min="2" max="2" width="38" style="37" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="37" customWidth="1"/>
-    <col min="4" max="4" width="19.8516" style="37" customWidth="1"/>
-    <col min="5" max="6" width="16.3516" style="37" customWidth="1"/>
-    <col min="7" max="16384" width="16.3516" style="37" customWidth="1"/>
+    <col min="1" max="1" width="19.6719" style="38" customWidth="1"/>
+    <col min="2" max="2" width="38" style="38" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="38" customWidth="1"/>
+    <col min="4" max="4" width="19.8516" style="38" customWidth="1"/>
+    <col min="5" max="6" width="16.3516" style="38" customWidth="1"/>
+    <col min="7" max="16384" width="16.3516" style="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.2" customHeight="1">
-      <c r="A1" t="s" s="38">
+      <c r="A1" t="s" s="39">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="40">
         <v>41</v>
       </c>
-      <c r="B1" t="s" s="39">
+      <c r="C1" t="s" s="41">
         <v>42</v>
       </c>
-      <c r="C1" t="s" s="40">
+      <c r="D1" t="s" s="24">
         <v>43</v>
       </c>
-      <c r="D1" t="s" s="23">
+      <c r="E1" t="s" s="24">
         <v>44</v>
       </c>
-      <c r="E1" t="s" s="23">
+      <c r="F1" t="s" s="24">
         <v>45</v>
-      </c>
-      <c r="F1" t="s" s="23">
-        <v>46</v>
       </c>
     </row>
     <row r="2" ht="13.2" customHeight="1">
       <c r="A2" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B2" t="s" s="41">
-        <v>47</v>
+      <c r="B2" t="s" s="42">
+        <v>46</v>
       </c>
       <c r="C2" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="D2" t="s" s="42">
+      <c r="D2" t="s" s="43">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="44">
         <v>48</v>
       </c>
-      <c r="E2" t="s" s="43">
-        <v>49</v>
+      <c r="F2" t="s" s="45">
+        <v>47</v>
       </c>
-      <c r="F2" t="s" s="44">
-        <v>48</v>
-      </c>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="49"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="49"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="50"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="50"/>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="50"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="49"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="50"/>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="50"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="49"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="50"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="49"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="50"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="49"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="49"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="50"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="50"/>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="50"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="49"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="50"/>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="50"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="49"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="50"/>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="50"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="49"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="50"/>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="50"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="49"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="50"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="49"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="50"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="49"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="50"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="49"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="50"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="49"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="50"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="49"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="50"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="49"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
     </row>
     <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="50"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="49"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
     </row>
     <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="50"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="49"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="50"/>
     </row>
     <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="50"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="49"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="50"/>
     </row>
     <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="50"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="49"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="50"/>
     </row>
     <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="50"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="49"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="50"/>
     </row>
     <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="50"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="49"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="50"/>
     </row>
     <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="50"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="50"/>
     </row>
     <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="50"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="49"/>
+      <c r="A29" s="51"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="50"/>
     </row>
     <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="50"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="49"/>
+      <c r="A30" s="51"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="50"/>
     </row>
     <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="50"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="49"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="50"/>
     </row>
     <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="50"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="49"/>
+      <c r="A32" s="51"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="50"/>
     </row>
     <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="50"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="49"/>
+      <c r="A33" s="51"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="50"/>
     </row>
     <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="50"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="49"/>
+      <c r="A34" s="51"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="50"/>
     </row>
     <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="50"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="49"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="50"/>
     </row>
     <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="50"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="49"/>
+      <c r="A36" s="51"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="50"/>
     </row>
     <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="50"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="49"/>
+      <c r="A37" s="51"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="50"/>
     </row>
     <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="50"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="49"/>
+      <c r="A38" s="51"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="50"/>
     </row>
     <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="50"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="49"/>
+      <c r="A39" s="51"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="50"/>
     </row>
     <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="50"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="49"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="50"/>
     </row>
     <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="50"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="49"/>
+      <c r="A41" s="51"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="50"/>
     </row>
     <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="50"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="49"/>
+      <c r="A42" s="51"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="50"/>
     </row>
     <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="50"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="49"/>
+      <c r="A43" s="51"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="50"/>
     </row>
     <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="50"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="49"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="50"/>
     </row>
     <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="50"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="49"/>
+      <c r="A45" s="51"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="50"/>
     </row>
     <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="50"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="49"/>
+      <c r="A46" s="51"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="50"/>
     </row>
     <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="50"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="49"/>
+      <c r="A47" s="51"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="50"/>
     </row>
     <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="50"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="49"/>
+      <c r="A48" s="51"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="50"/>
     </row>
     <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="50"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="49"/>
+      <c r="A49" s="51"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="51"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="54"/>
+      <c r="A50" s="52"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
